--- a/Automation Anywhere/Bots/TrivalentePolizas/Docs/Catalogos.xlsx
+++ b/Automation Anywhere/Bots/TrivalentePolizas/Docs/Catalogos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emergys1-my.sharepoint.com/personal/hector_agraz_emergys_com/Documents/PoC/trivalente/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="11_F25DC773A252ABDACC104837715E4E725BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B269C304-3304-48A8-B5EA-35E86930DE43}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="11_F25DC773A252ABDACC104837715E4E725BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96143EC7-BEA0-4AB7-8B52-6E9F92411D5A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>Key</t>
   </si>
@@ -48,18 +48,9 @@
     <t>GetComp</t>
   </si>
   <si>
-    <t>Obtener el listado de las empresas a diccionario</t>
-  </si>
-  <si>
     <t>LoginXML</t>
   </si>
   <si>
-    <t>Company</t>
-  </si>
-  <si>
-    <t>Empresa: {0}</t>
-  </si>
-  <si>
     <t>Ingresando al Aplicativo Descarga y administración Masiva de XML</t>
   </si>
   <si>
@@ -67,6 +58,87 @@
   </si>
   <si>
     <t>CloseXML</t>
+  </si>
+  <si>
+    <t>ErrorXML</t>
+  </si>
+  <si>
+    <t>LoginContpaqi</t>
+  </si>
+  <si>
+    <t>CloseContpaqi</t>
+  </si>
+  <si>
+    <t>Ingresando al Aplicativo Contpaqi</t>
+  </si>
+  <si>
+    <t>Cerrando Contpaqi</t>
+  </si>
+  <si>
+    <t>No se pudo abrir Contpaqi</t>
+  </si>
+  <si>
+    <t>No se pudo abrir Descarga y administración Masiva de XML</t>
+  </si>
+  <si>
+    <t>ErrorContpaqi</t>
+  </si>
+  <si>
+    <t>ErrorEmpresa</t>
+  </si>
+  <si>
+    <t>RFC De Empresa: {0}</t>
+  </si>
+  <si>
+    <t>No se pudo encontrar la empresa {0} en ContPaqi</t>
+  </si>
+  <si>
+    <t>LoadingEmitted</t>
+  </si>
+  <si>
+    <t>Empezando con la carga de XMLs emitidos</t>
+  </si>
+  <si>
+    <t>EnterPath</t>
+  </si>
+  <si>
+    <t>Ingresando ruta para abrir carpeta de XML{0}</t>
+  </si>
+  <si>
+    <t>LoadXMLs</t>
+  </si>
+  <si>
+    <t>CargandoXMLs</t>
+  </si>
+  <si>
+    <t>CompanyRFC</t>
+  </si>
+  <si>
+    <t>CompanyName</t>
+  </si>
+  <si>
+    <t>Nombre de la empresa: {0}</t>
+  </si>
+  <si>
+    <t>GetCompanyRFC</t>
+  </si>
+  <si>
+    <t>Obtener lista de RFC de empresas a diccionaroo</t>
+  </si>
+  <si>
+    <t>Obtener listado de nombre de empresas a diccionario</t>
+  </si>
+  <si>
+    <t>NoConsolidarte</t>
+  </si>
+  <si>
+    <t>No se encontro el archivo consolidado</t>
+  </si>
+  <si>
+    <t>Archivo validar {0}</t>
+  </si>
+  <si>
+    <t>SearhConsolidate</t>
   </si>
 </sst>
 </file>
@@ -429,13 +501,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="60.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -443,7 +516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -451,7 +524,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -459,64 +532,154 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="11:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
       <c r="K17" s="3"/>
     </row>
-    <row r="18" spans="11:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
       <c r="K18" s="3"/>
     </row>
-    <row r="19" spans="11:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K19" s="4"/>
-    </row>
-    <row r="20" spans="11:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="K19" s="3"/>
+    </row>
+    <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="K20" s="3"/>
     </row>
-    <row r="22" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K22" s="5"/>
+    <row r="21" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K21" s="3"/>
+    </row>
+    <row r="22" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K22" s="3"/>
+    </row>
+    <row r="23" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K23" s="4"/>
+    </row>
+    <row r="24" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K24" s="3"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K26" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Automation Anywhere/Bots/TrivalentePolizas/Docs/Catalogos.xlsx
+++ b/Automation Anywhere/Bots/TrivalentePolizas/Docs/Catalogos.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emergys1-my.sharepoint.com/personal/hector_agraz_emergys_com/Documents/PoC/trivalente/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="11_F25DC773A252ABDACC104837715E4E725BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96143EC7-BEA0-4AB7-8B52-6E9F92411D5A}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{F7C731B2-1FF6-47B4-BAC5-6BC2826A480D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C052993-C5CD-4E9A-B859-08A679074DC9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Logs" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
   <si>
     <t>Key</t>
   </si>
@@ -48,48 +59,78 @@
     <t>GetComp</t>
   </si>
   <si>
+    <t>Obtener listado de nombre de empresas a diccionario</t>
+  </si>
+  <si>
+    <t>GetCompanyRFC</t>
+  </si>
+  <si>
+    <t>Obtener lista de RFC de empresas a diccionaroo</t>
+  </si>
+  <si>
+    <t>CompanyRFC</t>
+  </si>
+  <si>
+    <t>RFC De Empresa: {0}</t>
+  </si>
+  <si>
+    <t>CompanyName</t>
+  </si>
+  <si>
+    <t>Nombre de la empresa: {0}</t>
+  </si>
+  <si>
+    <t>SearhConsolidate</t>
+  </si>
+  <si>
+    <t>Archivo validar {0}</t>
+  </si>
+  <si>
+    <t>NoConsolidarte</t>
+  </si>
+  <si>
+    <t>No se encontro el archivo consolidado</t>
+  </si>
+  <si>
     <t>LoginXML</t>
   </si>
   <si>
     <t>Ingresando al Aplicativo Descarga y administración Masiva de XML</t>
   </si>
   <si>
+    <t>CloseXML</t>
+  </si>
+  <si>
     <t>Cerrando Aplicativo Descarga y administración Masiva de XML</t>
   </si>
   <si>
-    <t>CloseXML</t>
-  </si>
-  <si>
     <t>ErrorXML</t>
   </si>
   <si>
+    <t>No se pudo abrir Descarga y administración Masiva de XML</t>
+  </si>
+  <si>
     <t>LoginContpaqi</t>
   </si>
   <si>
+    <t>Ingresando al Aplicativo Contpaqi</t>
+  </si>
+  <si>
     <t>CloseContpaqi</t>
   </si>
   <si>
-    <t>Ingresando al Aplicativo Contpaqi</t>
-  </si>
-  <si>
     <t>Cerrando Contpaqi</t>
   </si>
   <si>
+    <t>ErrorContpaqi</t>
+  </si>
+  <si>
     <t>No se pudo abrir Contpaqi</t>
   </si>
   <si>
-    <t>No se pudo abrir Descarga y administración Masiva de XML</t>
-  </si>
-  <si>
-    <t>ErrorContpaqi</t>
-  </si>
-  <si>
     <t>ErrorEmpresa</t>
   </si>
   <si>
-    <t>RFC De Empresa: {0}</t>
-  </si>
-  <si>
     <t>No se pudo encontrar la empresa {0} en ContPaqi</t>
   </si>
   <si>
@@ -108,44 +149,161 @@
     <t>LoadXMLs</t>
   </si>
   <si>
-    <t>CargandoXMLs</t>
-  </si>
-  <si>
-    <t>CompanyRFC</t>
-  </si>
-  <si>
-    <t>CompanyName</t>
-  </si>
-  <si>
-    <t>Nombre de la empresa: {0}</t>
-  </si>
-  <si>
-    <t>GetCompanyRFC</t>
-  </si>
-  <si>
-    <t>Obtener lista de RFC de empresas a diccionaroo</t>
-  </si>
-  <si>
-    <t>Obtener listado de nombre de empresas a diccionario</t>
-  </si>
-  <si>
-    <t>NoConsolidarte</t>
-  </si>
-  <si>
-    <t>No se encontro el archivo consolidado</t>
-  </si>
-  <si>
-    <t>Archivo validar {0}</t>
-  </si>
-  <si>
-    <t>SearhConsolidate</t>
+    <t>EndLoadXML</t>
+  </si>
+  <si>
+    <t>Termino de cargar XML</t>
+  </si>
+  <si>
+    <t>Cargando XMLs</t>
+  </si>
+  <si>
+    <t>TotalXMLs</t>
+  </si>
+  <si>
+    <t>Se cargaron un total de {0} Xmls</t>
+  </si>
+  <si>
+    <t>Se encontro error de clasificacion en el XML No:{0} UID:{1}</t>
+  </si>
+  <si>
+    <t>ErrorLoadedXML</t>
+  </si>
+  <si>
+    <t>GetPxXY</t>
+  </si>
+  <si>
+    <t>Click en datalles para tomar Screen Shoot con cordenadas {0}</t>
+  </si>
+  <si>
+    <t>ClicRow</t>
+  </si>
+  <si>
+    <t>Obtener codrenadas del boton detalle {0}</t>
+  </si>
+  <si>
+    <t>FilePath</t>
+  </si>
+  <si>
+    <t>Obteniendo ruta de archivo: {0}</t>
+  </si>
+  <si>
+    <t>DownloadXMLE</t>
+  </si>
+  <si>
+    <t>Descargar XML Emitidos</t>
+  </si>
+  <si>
+    <t>SetDate</t>
+  </si>
+  <si>
+    <t>Ingresando Fecha: {0}</t>
+  </si>
+  <si>
+    <t>ProcessSucces</t>
+  </si>
+  <si>
+    <t>ProcessError</t>
+  </si>
+  <si>
+    <t>Empresa se proceso correctamente {0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error al procesar Empresa con RFC: </t>
+  </si>
+  <si>
+    <t>Se encontraron {0} facturas</t>
+  </si>
+  <si>
+    <t>GenInvoice</t>
+  </si>
+  <si>
+    <t>CreatePolicy</t>
+  </si>
+  <si>
+    <t>Creacion de poliza</t>
+  </si>
+  <si>
+    <t>GetDatainvoice</t>
+  </si>
+  <si>
+    <t>Factura ya procesada</t>
+  </si>
+  <si>
+    <t>InvoiceProcess</t>
+  </si>
+  <si>
+    <t>NoInvoiceFound</t>
+  </si>
+  <si>
+    <t>CreditableCharge</t>
+  </si>
+  <si>
+    <t>CreditableAbono</t>
+  </si>
+  <si>
+    <t>RegisterAccountBank</t>
+  </si>
+  <si>
+    <t>Registrar movimiento a cuenta iva acreditable pagado en Cargo</t>
+  </si>
+  <si>
+    <t>Registrar movimient  a cuenta iva acreditable pagado en abono</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regitrar movimento a cuenta de Banco </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regitrar movimento a cuenta de factura </t>
+  </si>
+  <si>
+    <t>RegisterInvoice</t>
+  </si>
+  <si>
+    <t>Obteniendo datos, 
+Company Name: {5}
+Total Consecutive: {0}
+Type Policy: {1}
+Type REP: {8}
+Date: {2}
+Number Policy: {3}
+Folio: {4}
+Total: {6}
+UUID: {7}</t>
+  </si>
+  <si>
+    <t>Poliza Cero</t>
+  </si>
+  <si>
+    <t>PolicyCero</t>
+  </si>
+  <si>
+    <t>UUIDEmpty</t>
+  </si>
+  <si>
+    <t>Sin UUID</t>
+  </si>
+  <si>
+    <t>No se encontro factura</t>
+  </si>
+  <si>
+    <t>ErrorPolicy</t>
+  </si>
+  <si>
+    <t>Error al procesar Poliza</t>
+  </si>
+  <si>
+    <t>ErrorProv</t>
+  </si>
+  <si>
+    <t>Se hubo un proble al provesar las provisiones de ventas/gastos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -191,6 +349,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -213,13 +377,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -501,7 +669,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K26"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
@@ -537,151 +706,324 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
-      </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>24</v>
       </c>
       <c r="B18" t="s">
         <v>25</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>26</v>
       </c>
       <c r="B19" t="s">
         <v>27</v>
       </c>
-      <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K21" s="3"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="22" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" t="s">
+        <v>33</v>
+      </c>
       <c r="K22" s="3"/>
     </row>
     <row r="23" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="K23" s="4"/>
+      <c r="A23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" t="s">
+        <v>35</v>
+      </c>
+      <c r="K23" s="3"/>
     </row>
     <row r="24" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" t="s">
+        <v>39</v>
+      </c>
       <c r="K24" s="3"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K26" s="5"/>
+    <row r="25" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="K25" s="3"/>
+    </row>
+    <row r="26" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" t="s">
+        <v>41</v>
+      </c>
+      <c r="K26" s="3"/>
+    </row>
+    <row r="27" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" t="s">
+        <v>42</v>
+      </c>
+      <c r="K27" s="3"/>
+    </row>
+    <row r="28" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" t="s">
+        <v>47</v>
+      </c>
+      <c r="K28" s="4"/>
+    </row>
+    <row r="29" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="K29" s="3"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
+        <v>61</v>
+      </c>
+      <c r="K31" s="5"/>
+    </row>
+    <row r="32" spans="1:11" ht="150" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>83</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId1"/>
 </worksheet>
 </file>